--- a/Result/profitability/3447.xlsx
+++ b/Result/profitability/3447.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM47"/>
+  <dimension ref="A1:AM48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.08</v>
       </c>
       <c r="M2" t="n">
-        <v>0.575</v>
+        <v>0.4575</v>
       </c>
       <c r="N2" t="n">
-        <v>12.2075</v>
+        <v>11.56</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4275</v>
+        <v>0.3825</v>
       </c>
       <c r="N3" t="n">
-        <v>12.14625</v>
+        <v>11.57875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.97</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2325</v>
+        <v>0.21875</v>
       </c>
       <c r="N4" t="n">
-        <v>12.1725</v>
+        <v>11.54875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01250000000000001</v>
+        <v>0.05374999999999996</v>
       </c>
       <c r="N5" t="n">
-        <v>11.80125</v>
+        <v>11.71375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0.19125</v>
+        <v>0.06624999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>12.17</v>
+        <v>11.78625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.9</v>
       </c>
       <c r="M7" t="n">
-        <v>0.275</v>
+        <v>0.26375</v>
       </c>
       <c r="N7" t="n">
-        <v>12.71875</v>
+        <v>13.0425</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -6397,6 +6397,133 @@
       </c>
       <c r="AM47" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3447</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>855</v>
+      </c>
+      <c r="D48" t="n">
+        <v>776</v>
+      </c>
+      <c r="E48" t="n">
+        <v>79</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-2.04%</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>38</v>
+      </c>
+      <c r="J48" t="n">
+        <v>21</v>
+      </c>
+      <c r="K48" t="n">
+        <v>18</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="N48" t="n">
+        <v>11.22875</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.3529411764705881</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>-0.1799999999999997</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>-0.01914893617021274</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>-1.766666666666667</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>-0.6999999999999993</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>-0.07056451612903214</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK48" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
